--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179497</v>
+        <v>120181138</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -833,17 +833,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640519</v>
+        <v>640388</v>
       </c>
       <c r="R3" t="n">
-        <v>6555286</v>
+        <v>6555348</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181138</v>
+        <v>120180260</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,48 +921,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grönbrink, Srm</t>
+          <t>Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640388</v>
+        <v>640550</v>
       </c>
       <c r="R4" t="n">
-        <v>6555348</v>
+        <v>6555289</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1006,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180260</v>
+        <v>120179497</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,39 +1050,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640550</v>
+        <v>640519</v>
       </c>
       <c r="R5" t="n">
-        <v>6555289</v>
+        <v>6555286</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179183</v>
+        <v>120179497</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640623</v>
+        <v>640519</v>
       </c>
       <c r="R2" t="n">
-        <v>6555300</v>
+        <v>6555286</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181138</v>
+        <v>120180260</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,48 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönbrink, Srm</t>
+          <t>Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640388</v>
+        <v>640550</v>
       </c>
       <c r="R3" t="n">
-        <v>6555348</v>
+        <v>6555289</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120180260</v>
+        <v>120181138</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,53 +940,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640550</v>
+        <v>640388</v>
       </c>
       <c r="R4" t="n">
-        <v>6555289</v>
+        <v>6555348</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,12 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179497</v>
+        <v>120179183</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,33 +1059,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640519</v>
+        <v>640623</v>
       </c>
       <c r="R5" t="n">
-        <v>6555286</v>
+        <v>6555300</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1120,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179497</v>
+        <v>120179183</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640519</v>
+        <v>640623</v>
       </c>
       <c r="R2" t="n">
-        <v>6555286</v>
+        <v>6555300</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120180260</v>
+        <v>120181138</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,53 +802,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640550</v>
+        <v>640388</v>
       </c>
       <c r="R3" t="n">
-        <v>6555289</v>
+        <v>6555348</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181138</v>
+        <v>120179497</v>
       </c>
       <c r="B4" t="n">
         <v>91858</v>
@@ -971,17 +952,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grönbrink, Srm</t>
+          <t>Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640388</v>
+        <v>640519</v>
       </c>
       <c r="R4" t="n">
-        <v>6555348</v>
+        <v>6555286</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179183</v>
+        <v>120180260</v>
       </c>
       <c r="B5" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,30 +1045,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640623</v>
+        <v>640550</v>
       </c>
       <c r="R5" t="n">
-        <v>6555300</v>
+        <v>6555289</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179183</v>
+        <v>120179497</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640623</v>
+        <v>640519</v>
       </c>
       <c r="R2" t="n">
-        <v>6555300</v>
+        <v>6555286</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120181138</v>
+        <v>120180260</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,48 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönbrink, Srm</t>
+          <t>Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640388</v>
+        <v>640550</v>
       </c>
       <c r="R3" t="n">
-        <v>6555348</v>
+        <v>6555289</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179497</v>
+        <v>120179183</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,33 +940,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -956,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640519</v>
+        <v>640623</v>
       </c>
       <c r="R4" t="n">
-        <v>6555286</v>
+        <v>6555300</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -991,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180260</v>
+        <v>120181138</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,53 +1055,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640550</v>
+        <v>640388</v>
       </c>
       <c r="R5" t="n">
-        <v>6555289</v>
+        <v>6555348</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179497</v>
+        <v>120179183</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,33 +687,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640519</v>
+        <v>640623</v>
       </c>
       <c r="R2" t="n">
-        <v>6555286</v>
+        <v>6555300</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,12 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120180260</v>
+        <v>120179497</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +802,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640550</v>
+        <v>640519</v>
       </c>
       <c r="R3" t="n">
-        <v>6555289</v>
+        <v>6555286</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179183</v>
+        <v>120181138</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,44 +926,48 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640623</v>
+        <v>640388</v>
       </c>
       <c r="R4" t="n">
-        <v>6555300</v>
+        <v>6555348</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1006,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120181138</v>
+        <v>120180260</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,48 +1045,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grönbrink, Srm</t>
+          <t>Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640388</v>
+        <v>640550</v>
       </c>
       <c r="R5" t="n">
-        <v>6555348</v>
+        <v>6555289</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -790,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120179497</v>
+        <v>120181138</v>
       </c>
       <c r="B3" t="n">
         <v>91858</v>
@@ -833,17 +833,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640519</v>
+        <v>640388</v>
       </c>
       <c r="R3" t="n">
-        <v>6555286</v>
+        <v>6555348</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120181138</v>
+        <v>120180260</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,48 +921,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grönbrink, Srm</t>
+          <t>Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640388</v>
+        <v>640550</v>
       </c>
       <c r="R4" t="n">
-        <v>6555348</v>
+        <v>6555289</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1006,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180260</v>
+        <v>120179497</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,39 +1050,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640550</v>
+        <v>640519</v>
       </c>
       <c r="R5" t="n">
-        <v>6555289</v>
+        <v>6555286</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120180260</v>
+        <v>120179497</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,39 +921,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640550</v>
+        <v>640519</v>
       </c>
       <c r="R4" t="n">
-        <v>6555289</v>
+        <v>6555286</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,12 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120179497</v>
+        <v>120180260</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,34 +1045,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640519</v>
+        <v>640550</v>
       </c>
       <c r="R5" t="n">
-        <v>6555286</v>
+        <v>6555289</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120179183</v>
+        <v>120179497</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,29 +687,33 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640623</v>
+        <v>640519</v>
       </c>
       <c r="R2" t="n">
-        <v>6555300</v>
+        <v>6555286</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +767,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120179497</v>
+        <v>120179183</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,33 +930,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -956,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640519</v>
+        <v>640623</v>
       </c>
       <c r="R4" t="n">
-        <v>6555286</v>
+        <v>6555300</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -991,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar. Mellanskog planerar avverka på impediment, tallhällmark.</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,6 +1160,135 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121401037</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Älmsta, 700 m NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>640467</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6555317</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst en vinterståndare. Återfynd (Michael Lander, 90 ex. 241003). Dagens fynd är vid samma tall som på tidigare bilder, men koordinatpunkten ligger cirka 90 meter åt VNV. Det börjar skymma när jag till slut hittar rätt tall, så antalet skott kan vara betydligt fler.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Mossig, gles barrblandskog i nordostläge.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1289,6 +1289,580 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121434240</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>640418</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6555513</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121439066</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97035</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>640409</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6555499</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121433794</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>640379</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6555397</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121436238</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Älmsta, Älmsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>640593</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6555301</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121434294</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Älmsta, Älmsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>640414</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6555503</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121434240</v>
+        <v>121432972</v>
       </c>
       <c r="B7" t="n">
-        <v>8421</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,38 +1303,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640418</v>
+        <v>640464</v>
       </c>
       <c r="R7" t="n">
-        <v>6555513</v>
+        <v>6555319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1366,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1392,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,6 +1406,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1396,17 +1418,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121439066</v>
+        <v>121432783</v>
       </c>
       <c r="B8" t="n">
-        <v>97035</v>
+        <v>91973</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1419,34 +1441,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640409</v>
+        <v>640466</v>
       </c>
       <c r="R8" t="n">
-        <v>6555499</v>
+        <v>6555324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1503,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1488,7 +1513,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,6 +1522,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1508,17 +1534,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121433794</v>
+        <v>121439066</v>
       </c>
       <c r="B9" t="n">
-        <v>8421</v>
+        <v>97035</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1531,34 +1557,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640379</v>
+        <v>640409</v>
       </c>
       <c r="R9" t="n">
-        <v>6555397</v>
+        <v>6555499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1620,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,7 +1630,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,6 +1639,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1620,14 +1651,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121436238</v>
+        <v>121432726</v>
       </c>
       <c r="B10" t="n">
         <v>91973</v>
@@ -1661,16 +1692,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640593</v>
+        <v>640426</v>
       </c>
       <c r="R10" t="n">
-        <v>6555301</v>
+        <v>6555326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,7 +1736,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1746,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,6 +1755,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1732,7 +1767,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1787,6 +1822,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Älmsta, Älmsta, Srm</t>
@@ -1841,12 +1878,18 @@
           <t>12:08</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1858,10 +1901,362 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121434240</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>640418</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6555513</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121436238</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91973</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Älmsta, Älmsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>640593</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6555301</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121433794</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8421</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>640379</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6555397</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120180260</v>
+        <v>121401037</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1068,27 +1068,31 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Älmsta, Srm</t>
+          <t>Älmsta, 700 m NNV om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640550</v>
+        <v>640467</v>
       </c>
       <c r="R5" t="n">
-        <v>6555289</v>
+        <v>6555317</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1115,27 +1119,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>Minst en vinterståndare. Återfynd (Michael Lander, 90 ex. 241003). Dagens fynd är vid samma tall som på tidigare bilder, men koordinatpunkten ligger cirka 90 meter åt VNV. Det börjar skymma när jag till slut hittar rätt tall, så antalet skott kan vara betydligt fler.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,28 +1138,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Mossig, gles barrblandskog i nordostläge.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121401037</v>
+        <v>121326333</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,34 +1197,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älmsta, 700 m NNV om, Srm</t>
+          <t>Älmsta  (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640467</v>
+        <v>640550</v>
       </c>
       <c r="R6" t="n">
-        <v>6555317</v>
+        <v>6555289</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1246,19 +1239,24 @@
           <t>Överjärna</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>AB-Söd-0311</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst en vinterståndare. Återfynd (Michael Lander, 90 ex. 241003). Dagens fynd är vid samma tall som på tidigare bilder, men koordinatpunkten ligger cirka 90 meter åt VNV. Det börjar skymma när jag till slut hittar rätt tall, så antalet skott kan vara betydligt fler.</t>
+          <t>Älmsta, Obskoord: 6555862/1594497/5 m (). Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1267,34 +1265,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Mossig, gles barrblandskog i nordostläge.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121432972</v>
+        <v>121434240</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>8421</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,54 +1299,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640464</v>
+        <v>640418</v>
       </c>
       <c r="R7" t="n">
-        <v>6555319</v>
+        <v>6555513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1382,7 +1367,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1392,12 +1377,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432783</v>
+        <v>121432972</v>
       </c>
       <c r="B8" t="n">
-        <v>91973</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,41 +1417,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640466</v>
+        <v>640464</v>
       </c>
       <c r="R8" t="n">
-        <v>6555324</v>
+        <v>6555319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1503,7 +1496,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1513,7 +1506,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121439066</v>
+        <v>121432783</v>
       </c>
       <c r="B9" t="n">
-        <v>97035</v>
+        <v>91985</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1557,27 +1555,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1585,10 +1582,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640409</v>
+        <v>640466</v>
       </c>
       <c r="R9" t="n">
-        <v>6555499</v>
+        <v>6555324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,7 +1617,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1630,7 +1627,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,7 +1658,7 @@
         <v>121432726</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1774,10 +1771,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121434294</v>
+        <v>121436238</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>91985</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1786,43 +1783,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1830,10 +1814,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640414</v>
+        <v>640593</v>
       </c>
       <c r="R11" t="n">
-        <v>6555503</v>
+        <v>6555301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1865,7 +1849,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1875,12 +1859,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,10 +1887,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121434240</v>
+        <v>121434294</v>
       </c>
       <c r="B12" t="n">
-        <v>8421</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,43 +1899,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640418</v>
+        <v>640414</v>
       </c>
       <c r="R12" t="n">
-        <v>6555513</v>
+        <v>6555503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1988,7 +1978,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1998,7 +1988,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,10 +2021,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121436238</v>
+        <v>121433794</v>
       </c>
       <c r="B13" t="n">
-        <v>91973</v>
+        <v>8421</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2042,37 +2037,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640593</v>
+        <v>640379</v>
       </c>
       <c r="R13" t="n">
-        <v>6555301</v>
+        <v>6555397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,7 +2101,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2114,7 +2111,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121433794</v>
+        <v>121439066</v>
       </c>
       <c r="B14" t="n">
-        <v>8421</v>
+        <v>97048</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2158,28 +2155,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2187,10 +2183,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>640379</v>
+        <v>640409</v>
       </c>
       <c r="R14" t="n">
-        <v>6555397</v>
+        <v>6555499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2222,7 +2218,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2232,7 +2228,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2257,6 +2253,130 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121474399</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97048</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Älmsta, NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>640443</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6555493</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tämligen tätt bestånd på något fuktig mark intill bäck.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,7 +1036,7 @@
         <v>121401037</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121326333</v>
+        <v>121432783</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,47 +1174,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älmsta  (*knärot* /stjälk/), Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640550</v>
+        <v>640466</v>
       </c>
       <c r="R6" t="n">
-        <v>6555289</v>
+        <v>6555324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,24 +1233,24 @@
           <t>Överjärna</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>AB-Söd-0311</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Älmsta, Obskoord: 6555862/1594497/5 m (). Nära hundra plantor inom en kvadratmeter. Strax nedanför hällmark i ett granbestånd. Skuggig plats. Mellanskog planerar avverka skogsområdet.</t>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,32 +1259,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121434240</v>
+        <v>121436238</v>
       </c>
       <c r="B7" t="n">
-        <v>8421</v>
+        <v>91986</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,39 +1294,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640418</v>
+        <v>640593</v>
       </c>
       <c r="R7" t="n">
-        <v>6555513</v>
+        <v>6555301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1367,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1377,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432972</v>
+        <v>121434240</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>8421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,54 +1406,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640464</v>
+        <v>640418</v>
       </c>
       <c r="R8" t="n">
-        <v>6555319</v>
+        <v>6555513</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,12 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432783</v>
+        <v>121439066</v>
       </c>
       <c r="B9" t="n">
-        <v>91985</v>
+        <v>97049</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,26 +1528,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1582,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640466</v>
+        <v>640409</v>
       </c>
       <c r="R9" t="n">
-        <v>6555324</v>
+        <v>6555499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1617,7 +1591,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1627,7 +1601,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121432726</v>
+        <v>121433794</v>
       </c>
       <c r="B10" t="n">
-        <v>91985</v>
+        <v>8421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1671,26 +1645,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1698,10 +1674,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640426</v>
+        <v>640379</v>
       </c>
       <c r="R10" t="n">
-        <v>6555326</v>
+        <v>6555397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1733,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1743,7 +1719,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121436238</v>
+        <v>121432726</v>
       </c>
       <c r="B11" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1810,14 +1786,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640593</v>
+        <v>640426</v>
       </c>
       <c r="R11" t="n">
-        <v>6555301</v>
+        <v>6555326</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1835,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,7 +1866,7 @@
         <v>121434294</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2021,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121433794</v>
+        <v>121432972</v>
       </c>
       <c r="B13" t="n">
-        <v>8421</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2033,43 +2009,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640379</v>
+        <v>640464</v>
       </c>
       <c r="R13" t="n">
-        <v>6555397</v>
+        <v>6555319</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2101,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2111,7 +2098,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121439066</v>
+        <v>121474399</v>
       </c>
       <c r="B14" t="n">
-        <v>97048</v>
+        <v>97049</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2172,24 +2164,36 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, NNV om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>640409</v>
+        <v>640443</v>
       </c>
       <c r="R14" t="n">
-        <v>6555499</v>
+        <v>6555493</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2216,19 +2220,14 @@
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:27</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:27</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tämligen tätt bestånd på något fuktig mark intill bäck.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,139 +2243,15 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Rolf Wahlström, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121474399</v>
-      </c>
-      <c r="B15" t="n">
-        <v>97048</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Älmsta, NNV om, Srm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>640443</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6555493</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Södertälje</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Överjärna</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-12-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tämligen tätt bestånd på något fuktig mark intill bäck.</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>121401037</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121432783</v>
+        <v>121434240</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>8424</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,26 +1178,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640466</v>
+        <v>640418</v>
       </c>
       <c r="R6" t="n">
-        <v>6555324</v>
+        <v>6555513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121436238</v>
+        <v>121432726</v>
       </c>
       <c r="B7" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,14 +1319,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640593</v>
+        <v>640426</v>
       </c>
       <c r="R7" t="n">
-        <v>6555301</v>
+        <v>6555326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121434240</v>
+        <v>121432972</v>
       </c>
       <c r="B8" t="n">
-        <v>8421</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,43 +1408,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640418</v>
+        <v>640464</v>
       </c>
       <c r="R8" t="n">
-        <v>6555513</v>
+        <v>6555319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,7 +1487,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1497,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121439066</v>
+        <v>121432783</v>
       </c>
       <c r="B9" t="n">
-        <v>97049</v>
+        <v>91989</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,27 +1546,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1556,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640409</v>
+        <v>640466</v>
       </c>
       <c r="R9" t="n">
-        <v>6555499</v>
+        <v>6555324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1608,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1618,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121433794</v>
+        <v>121439066</v>
       </c>
       <c r="B10" t="n">
-        <v>8421</v>
+        <v>97052</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,28 +1662,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1674,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640379</v>
+        <v>640409</v>
       </c>
       <c r="R10" t="n">
-        <v>6555397</v>
+        <v>6555499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121432726</v>
+        <v>121433794</v>
       </c>
       <c r="B11" t="n">
-        <v>91986</v>
+        <v>8424</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,26 +1779,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1790,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640426</v>
+        <v>640379</v>
       </c>
       <c r="R11" t="n">
-        <v>6555326</v>
+        <v>6555397</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1843,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1853,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121434294</v>
+        <v>121436238</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,43 +1893,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1919,10 +1924,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640414</v>
+        <v>640593</v>
       </c>
       <c r="R12" t="n">
-        <v>6555503</v>
+        <v>6555301</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,12 +1969,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121432972</v>
+        <v>121434294</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640464</v>
+        <v>640414</v>
       </c>
       <c r="R13" t="n">
-        <v>6555319</v>
+        <v>6555503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,7 +2134,7 @@
         <v>121474399</v>
       </c>
       <c r="B14" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121434240</v>
+        <v>121432783</v>
       </c>
       <c r="B6" t="n">
-        <v>8424</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,28 +1178,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640418</v>
+        <v>640466</v>
       </c>
       <c r="R6" t="n">
-        <v>6555513</v>
+        <v>6555324</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121432726</v>
+        <v>121434240</v>
       </c>
       <c r="B7" t="n">
-        <v>91989</v>
+        <v>8424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,26 +1294,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640426</v>
+        <v>640418</v>
       </c>
       <c r="R7" t="n">
-        <v>6555326</v>
+        <v>6555513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432783</v>
+        <v>121434294</v>
       </c>
       <c r="B9" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,41 +1542,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640466</v>
+        <v>640414</v>
       </c>
       <c r="R9" t="n">
-        <v>6555324</v>
+        <v>6555503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,7 +1621,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1618,7 +1631,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121439066</v>
+        <v>121432726</v>
       </c>
       <c r="B10" t="n">
-        <v>97052</v>
+        <v>91989</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,27 +1680,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1690,10 +1707,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640409</v>
+        <v>640426</v>
       </c>
       <c r="R10" t="n">
-        <v>6555499</v>
+        <v>6555326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1725,7 +1742,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1752,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,10 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121436238</v>
+        <v>121439066</v>
       </c>
       <c r="B12" t="n">
-        <v>91989</v>
+        <v>97052</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,37 +1914,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640593</v>
+        <v>640409</v>
       </c>
       <c r="R12" t="n">
-        <v>6555301</v>
+        <v>6555499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1959,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1969,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,10 +2015,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121434294</v>
+        <v>121436238</v>
       </c>
       <c r="B13" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2009,43 +2027,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2053,10 +2058,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640414</v>
+        <v>640593</v>
       </c>
       <c r="R13" t="n">
-        <v>6555503</v>
+        <v>6555301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2088,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,12 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,6 +2253,469 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121551458</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57508</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>640527</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6555570</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121551556</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8424</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>640504</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6555547</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121552781</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57508</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>640380</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6555545</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121551416</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grönbrink, Grönbrink, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>640552</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6555567</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överjärna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>121401037</v>
       </c>
       <c r="B5" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121432783</v>
+        <v>121433794</v>
       </c>
       <c r="B6" t="n">
-        <v>91989</v>
+        <v>8424</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,26 +1178,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640466</v>
+        <v>640379</v>
       </c>
       <c r="R6" t="n">
-        <v>6555324</v>
+        <v>6555397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432972</v>
+        <v>121434294</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,7 +1433,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1441,7 +1443,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1452,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640464</v>
+        <v>640414</v>
       </c>
       <c r="R8" t="n">
-        <v>6555319</v>
+        <v>6555503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1532,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121434294</v>
+        <v>121432972</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,7 +1567,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1575,7 +1577,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1586,10 +1588,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640414</v>
+        <v>640464</v>
       </c>
       <c r="R9" t="n">
-        <v>6555503</v>
+        <v>6555319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1623,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,12 +1633,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121432726</v>
+        <v>121432783</v>
       </c>
       <c r="B10" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1707,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640426</v>
+        <v>640466</v>
       </c>
       <c r="R10" t="n">
-        <v>6555326</v>
+        <v>6555324</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,7 +1744,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1752,7 +1754,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121433794</v>
+        <v>121439066</v>
       </c>
       <c r="B11" t="n">
-        <v>8424</v>
+        <v>97058</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,28 +1798,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1825,10 +1826,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640379</v>
+        <v>640409</v>
       </c>
       <c r="R11" t="n">
-        <v>6555397</v>
+        <v>6555499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1860,7 +1861,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1871,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121439066</v>
+        <v>121432726</v>
       </c>
       <c r="B12" t="n">
-        <v>97052</v>
+        <v>91995</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,27 +1915,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640409</v>
+        <v>640426</v>
       </c>
       <c r="R12" t="n">
-        <v>6555499</v>
+        <v>6555326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,7 +2018,7 @@
         <v>121436238</v>
       </c>
       <c r="B13" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>121474399</v>
       </c>
       <c r="B14" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121551556</v>
+        <v>121551416</v>
       </c>
       <c r="B16" t="n">
-        <v>8424</v>
+        <v>57371</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2384,38 +2384,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640504</v>
+        <v>640552</v>
       </c>
       <c r="R16" t="n">
-        <v>6555547</v>
+        <v>6555567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2447,7 +2452,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2457,7 +2462,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2601,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121551416</v>
+        <v>121551556</v>
       </c>
       <c r="B18" t="n">
-        <v>57371</v>
+        <v>8424</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2613,43 +2618,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640552</v>
+        <v>640504</v>
       </c>
       <c r="R18" t="n">
-        <v>6555567</v>
+        <v>6555547</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>121401037</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121433794</v>
+        <v>121432726</v>
       </c>
       <c r="B6" t="n">
-        <v>8424</v>
+        <v>91996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,28 +1178,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640379</v>
+        <v>640426</v>
       </c>
       <c r="R6" t="n">
-        <v>6555397</v>
+        <v>6555326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121434240</v>
+        <v>121434294</v>
       </c>
       <c r="B7" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,43 +1290,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640418</v>
+        <v>640414</v>
       </c>
       <c r="R7" t="n">
-        <v>6555513</v>
+        <v>6555503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1369,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1379,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121434294</v>
+        <v>121433794</v>
       </c>
       <c r="B8" t="n">
-        <v>98104</v>
+        <v>8424</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1410,54 +1424,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640414</v>
+        <v>640379</v>
       </c>
       <c r="R8" t="n">
-        <v>6555503</v>
+        <v>6555397</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1489,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,12 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,7 +1533,7 @@
         <v>121432972</v>
       </c>
       <c r="B9" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1669,7 +1667,7 @@
         <v>121432783</v>
       </c>
       <c r="B10" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1782,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121439066</v>
+        <v>121434240</v>
       </c>
       <c r="B11" t="n">
-        <v>97058</v>
+        <v>8424</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,27 +1796,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1826,10 +1825,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640409</v>
+        <v>640418</v>
       </c>
       <c r="R11" t="n">
-        <v>6555499</v>
+        <v>6555513</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1861,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1871,7 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,10 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121432726</v>
+        <v>121439066</v>
       </c>
       <c r="B12" t="n">
-        <v>91995</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,26 +1914,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640426</v>
+        <v>640409</v>
       </c>
       <c r="R12" t="n">
-        <v>6555326</v>
+        <v>6555499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,7 +2018,7 @@
         <v>121436238</v>
       </c>
       <c r="B13" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>121474399</v>
       </c>
       <c r="B14" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121551458</v>
+        <v>121551416</v>
       </c>
       <c r="B15" t="n">
-        <v>57508</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640527</v>
+        <v>640552</v>
       </c>
       <c r="R15" t="n">
-        <v>6555570</v>
+        <v>6555567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121551416</v>
+        <v>121551458</v>
       </c>
       <c r="B16" t="n">
-        <v>57371</v>
+        <v>57509</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,27 +2388,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640552</v>
+        <v>640527</v>
       </c>
       <c r="R16" t="n">
-        <v>6555567</v>
+        <v>6555570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121552781</v>
+        <v>121551556</v>
       </c>
       <c r="B17" t="n">
-        <v>57508</v>
+        <v>8424</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,43 +2501,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640380</v>
+        <v>640504</v>
       </c>
       <c r="R17" t="n">
-        <v>6555545</v>
+        <v>6555547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2574,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121551556</v>
+        <v>121552781</v>
       </c>
       <c r="B18" t="n">
-        <v>8424</v>
+        <v>57509</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,38 +2613,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640504</v>
+        <v>640380</v>
       </c>
       <c r="R18" t="n">
-        <v>6555547</v>
+        <v>6555545</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121432726</v>
+        <v>121433794</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>8424</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,26 +1178,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1205,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640426</v>
+        <v>640379</v>
       </c>
       <c r="R6" t="n">
-        <v>6555326</v>
+        <v>6555397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,7 +1280,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121434294</v>
+        <v>121432972</v>
       </c>
       <c r="B7" t="n">
         <v>98105</v>
@@ -1313,7 +1315,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1323,7 +1325,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1334,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640414</v>
+        <v>640464</v>
       </c>
       <c r="R7" t="n">
-        <v>6555503</v>
+        <v>6555319</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1379,12 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1412,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121433794</v>
+        <v>121432783</v>
       </c>
       <c r="B8" t="n">
-        <v>8424</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,28 +1430,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640379</v>
+        <v>640466</v>
       </c>
       <c r="R8" t="n">
-        <v>6555397</v>
+        <v>6555324</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432972</v>
+        <v>121434240</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>8424</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,54 +1542,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640464</v>
+        <v>640418</v>
       </c>
       <c r="R9" t="n">
-        <v>6555319</v>
+        <v>6555513</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,12 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1648,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121432783</v>
+        <v>121432726</v>
       </c>
       <c r="B10" t="n">
         <v>91996</v>
@@ -1707,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640466</v>
+        <v>640426</v>
       </c>
       <c r="R10" t="n">
-        <v>6555324</v>
+        <v>6555326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1742,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1752,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,10 +1764,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121434240</v>
+        <v>121434294</v>
       </c>
       <c r="B11" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1792,43 +1776,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640418</v>
+        <v>640414</v>
       </c>
       <c r="R11" t="n">
-        <v>6555513</v>
+        <v>6555503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1860,7 +1855,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1870,7 +1865,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121439066</v>
+        <v>121436238</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>91996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,38 +1914,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640409</v>
+        <v>640593</v>
       </c>
       <c r="R12" t="n">
-        <v>6555499</v>
+        <v>6555301</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1976,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1986,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,10 +2014,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121436238</v>
+        <v>121439066</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>97059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2031,37 +2030,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640593</v>
+        <v>640409</v>
       </c>
       <c r="R13" t="n">
-        <v>6555301</v>
+        <v>6555499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121551416</v>
+        <v>121551458</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640552</v>
+        <v>640527</v>
       </c>
       <c r="R15" t="n">
-        <v>6555567</v>
+        <v>6555570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121551458</v>
+        <v>121552781</v>
       </c>
       <c r="B16" t="n">
         <v>57509</v>
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640527</v>
+        <v>640380</v>
       </c>
       <c r="R16" t="n">
-        <v>6555570</v>
+        <v>6555545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121551556</v>
+        <v>121551416</v>
       </c>
       <c r="B17" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,38 +2501,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640504</v>
+        <v>640552</v>
       </c>
       <c r="R17" t="n">
-        <v>6555547</v>
+        <v>6555567</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2564,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2574,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121552781</v>
+        <v>121551556</v>
       </c>
       <c r="B18" t="n">
-        <v>57509</v>
+        <v>8424</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2613,43 +2618,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640380</v>
+        <v>640504</v>
       </c>
       <c r="R18" t="n">
-        <v>6555545</v>
+        <v>6555547</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121433794</v>
+        <v>121432972</v>
       </c>
       <c r="B6" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,43 +1174,54 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640379</v>
+        <v>640464</v>
       </c>
       <c r="R6" t="n">
-        <v>6555397</v>
+        <v>6555319</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1263,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121432972</v>
+        <v>121434240</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>8424</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,54 +1308,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640464</v>
+        <v>640418</v>
       </c>
       <c r="R7" t="n">
-        <v>6555319</v>
+        <v>6555513</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1376,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1386,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121432783</v>
+        <v>121434294</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,41 +1426,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640466</v>
+        <v>640414</v>
       </c>
       <c r="R8" t="n">
-        <v>6555324</v>
+        <v>6555503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1505,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1515,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121434240</v>
+        <v>121432783</v>
       </c>
       <c r="B9" t="n">
-        <v>8424</v>
+        <v>91996</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,28 +1564,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1575,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640418</v>
+        <v>640466</v>
       </c>
       <c r="R9" t="n">
-        <v>6555513</v>
+        <v>6555324</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1610,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121432726</v>
+        <v>121433794</v>
       </c>
       <c r="B10" t="n">
-        <v>91996</v>
+        <v>8424</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,26 +1680,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1691,10 +1709,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640426</v>
+        <v>640379</v>
       </c>
       <c r="R10" t="n">
-        <v>6555326</v>
+        <v>6555397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,7 +1744,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1754,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121434294</v>
+        <v>121432726</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1776,54 +1794,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640414</v>
+        <v>640426</v>
       </c>
       <c r="R11" t="n">
-        <v>6555503</v>
+        <v>6555326</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1855,7 +1860,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1865,12 +1870,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,10 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121436238</v>
+        <v>121439066</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,37 +1914,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640593</v>
+        <v>640409</v>
       </c>
       <c r="R12" t="n">
-        <v>6555301</v>
+        <v>6555499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1986,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2014,10 +2015,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121439066</v>
+        <v>121436238</v>
       </c>
       <c r="B13" t="n">
-        <v>97059</v>
+        <v>91996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,38 +2031,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640409</v>
+        <v>640593</v>
       </c>
       <c r="R13" t="n">
-        <v>6555499</v>
+        <v>6555301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121551458</v>
+        <v>121551416</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640527</v>
+        <v>640552</v>
       </c>
       <c r="R15" t="n">
-        <v>6555570</v>
+        <v>6555567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121551416</v>
+        <v>121551458</v>
       </c>
       <c r="B17" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,27 +2505,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640552</v>
+        <v>640527</v>
       </c>
       <c r="R17" t="n">
-        <v>6555567</v>
+        <v>6555570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121432972</v>
+        <v>121434240</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>8424</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,54 +1174,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640464</v>
+        <v>640418</v>
       </c>
       <c r="R6" t="n">
-        <v>6555319</v>
+        <v>6555513</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1253,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,12 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121434240</v>
+        <v>121434294</v>
       </c>
       <c r="B7" t="n">
-        <v>8424</v>
+        <v>98105</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,43 +1292,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640418</v>
+        <v>640414</v>
       </c>
       <c r="R7" t="n">
-        <v>6555513</v>
+        <v>6555503</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1376,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1386,7 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121434294</v>
+        <v>121436238</v>
       </c>
       <c r="B8" t="n">
-        <v>98105</v>
+        <v>91996</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,43 +1426,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1470,10 +1457,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640414</v>
+        <v>640593</v>
       </c>
       <c r="R8" t="n">
-        <v>6555503</v>
+        <v>6555301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,7 +1492,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1515,12 +1502,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432783</v>
+        <v>121432972</v>
       </c>
       <c r="B9" t="n">
-        <v>91996</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,41 +1542,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640466</v>
+        <v>640464</v>
       </c>
       <c r="R9" t="n">
-        <v>6555324</v>
+        <v>6555319</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1626,7 +1621,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1636,7 +1631,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121433794</v>
+        <v>121439066</v>
       </c>
       <c r="B10" t="n">
-        <v>8424</v>
+        <v>97059</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,28 +1680,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1709,10 +1708,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640379</v>
+        <v>640409</v>
       </c>
       <c r="R10" t="n">
-        <v>6555397</v>
+        <v>6555499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1744,7 +1743,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1754,7 +1753,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1898,10 +1897,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121439066</v>
+        <v>121432783</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>91996</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,27 +1913,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1942,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640409</v>
+        <v>640466</v>
       </c>
       <c r="R12" t="n">
-        <v>6555499</v>
+        <v>6555324</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2015,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121436238</v>
+        <v>121433794</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>8424</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2031,37 +2029,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640593</v>
+        <v>640379</v>
       </c>
       <c r="R13" t="n">
-        <v>6555301</v>
+        <v>6555397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121551416</v>
+        <v>121551458</v>
       </c>
       <c r="B15" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640552</v>
+        <v>640527</v>
       </c>
       <c r="R15" t="n">
-        <v>6555567</v>
+        <v>6555570</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121551458</v>
+        <v>121551556</v>
       </c>
       <c r="B17" t="n">
-        <v>57509</v>
+        <v>8424</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,43 +2501,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640527</v>
+        <v>640504</v>
       </c>
       <c r="R17" t="n">
-        <v>6555570</v>
+        <v>6555547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2574,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121551556</v>
+        <v>121551416</v>
       </c>
       <c r="B18" t="n">
-        <v>8424</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,38 +2613,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640504</v>
+        <v>640552</v>
       </c>
       <c r="R18" t="n">
-        <v>6555547</v>
+        <v>6555567</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1781,7 +1781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121432726</v>
+        <v>121432783</v>
       </c>
       <c r="B11" t="n">
         <v>91996</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640426</v>
+        <v>640466</v>
       </c>
       <c r="R11" t="n">
-        <v>6555326</v>
+        <v>6555324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,7 +1897,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121432783</v>
+        <v>121432726</v>
       </c>
       <c r="B12" t="n">
         <v>91996</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640466</v>
+        <v>640426</v>
       </c>
       <c r="R12" t="n">
-        <v>6555324</v>
+        <v>6555326</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1781,7 +1781,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121432783</v>
+        <v>121432726</v>
       </c>
       <c r="B11" t="n">
         <v>91996</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640466</v>
+        <v>640426</v>
       </c>
       <c r="R11" t="n">
-        <v>6555324</v>
+        <v>6555326</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,7 +1897,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121432726</v>
+        <v>121432783</v>
       </c>
       <c r="B12" t="n">
         <v>91996</v>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640426</v>
+        <v>640466</v>
       </c>
       <c r="R12" t="n">
-        <v>6555326</v>
+        <v>6555324</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1036,7 +1036,7 @@
         <v>121401037</v>
       </c>
       <c r="B5" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121434240</v>
+        <v>121436238</v>
       </c>
       <c r="B6" t="n">
-        <v>8424</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,39 +1178,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640418</v>
+        <v>640593</v>
       </c>
       <c r="R6" t="n">
-        <v>6555513</v>
+        <v>6555301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121434294</v>
+        <v>121432726</v>
       </c>
       <c r="B7" t="n">
-        <v>98105</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,54 +1290,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640414</v>
+        <v>640426</v>
       </c>
       <c r="R7" t="n">
-        <v>6555503</v>
+        <v>6555326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121436238</v>
+        <v>121432972</v>
       </c>
       <c r="B8" t="n">
-        <v>91996</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,30 +1406,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1457,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640593</v>
+        <v>640464</v>
       </c>
       <c r="R8" t="n">
-        <v>6555301</v>
+        <v>6555319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1502,7 +1495,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1528,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121432972</v>
+        <v>121439066</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,54 +1540,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640464</v>
+        <v>640409</v>
       </c>
       <c r="R9" t="n">
-        <v>6555319</v>
+        <v>6555499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1621,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,12 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121439066</v>
+        <v>121434240</v>
       </c>
       <c r="B10" t="n">
-        <v>97059</v>
+        <v>8425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1680,27 +1661,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1708,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640409</v>
+        <v>640418</v>
       </c>
       <c r="R10" t="n">
-        <v>6555499</v>
+        <v>6555513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1743,7 +1725,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1753,7 +1735,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1781,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121432726</v>
+        <v>121432783</v>
       </c>
       <c r="B11" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1824,10 +1806,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640426</v>
+        <v>640466</v>
       </c>
       <c r="R11" t="n">
-        <v>6555326</v>
+        <v>6555324</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1859,7 +1841,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1869,7 +1851,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1897,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121432783</v>
+        <v>121433794</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>8425</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1913,26 +1895,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1940,10 +1924,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640466</v>
+        <v>640379</v>
       </c>
       <c r="R12" t="n">
-        <v>6555324</v>
+        <v>6555397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1959,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1969,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,10 +1997,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121433794</v>
+        <v>121434294</v>
       </c>
       <c r="B13" t="n">
-        <v>8424</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2025,43 +2009,54 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640379</v>
+        <v>640414</v>
       </c>
       <c r="R13" t="n">
-        <v>6555397</v>
+        <v>6555503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2093,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2103,7 +2098,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,7 +2134,7 @@
         <v>121474399</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121551458</v>
+        <v>121551416</v>
       </c>
       <c r="B15" t="n">
-        <v>57509</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640527</v>
+        <v>640552</v>
       </c>
       <c r="R15" t="n">
-        <v>6555570</v>
+        <v>6555567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121552781</v>
+        <v>121551556</v>
       </c>
       <c r="B16" t="n">
-        <v>57509</v>
+        <v>8425</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2384,43 +2384,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640380</v>
+        <v>640504</v>
       </c>
       <c r="R16" t="n">
-        <v>6555545</v>
+        <v>6555547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121551556</v>
+        <v>121551458</v>
       </c>
       <c r="B17" t="n">
-        <v>8424</v>
+        <v>57510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2501,38 +2496,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640504</v>
+        <v>640527</v>
       </c>
       <c r="R17" t="n">
-        <v>6555547</v>
+        <v>6555570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121551416</v>
+        <v>121552781</v>
       </c>
       <c r="B18" t="n">
-        <v>57372</v>
+        <v>57510</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2617,27 +2617,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2646,10 +2646,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640552</v>
+        <v>640380</v>
       </c>
       <c r="R18" t="n">
-        <v>6555567</v>
+        <v>6555545</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -1162,7 +1162,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121432783</v>
+        <v>121432726</v>
       </c>
       <c r="B6" t="n">
         <v>92004</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640466</v>
+        <v>640426</v>
       </c>
       <c r="R6" t="n">
-        <v>6555324</v>
+        <v>6555326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121433794</v>
+        <v>121432783</v>
       </c>
       <c r="B7" t="n">
-        <v>8425</v>
+        <v>92004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,28 +1294,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1323,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640379</v>
+        <v>640466</v>
       </c>
       <c r="R7" t="n">
-        <v>6555397</v>
+        <v>6555324</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1368,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1394,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121434240</v>
+        <v>121436238</v>
       </c>
       <c r="B8" t="n">
-        <v>8425</v>
+        <v>92004</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,39 +1410,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640418</v>
+        <v>640593</v>
       </c>
       <c r="R8" t="n">
-        <v>6555513</v>
+        <v>6555301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1476,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1482,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121436238</v>
+        <v>121433794</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>8425</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1530,37 +1526,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640593</v>
+        <v>640379</v>
       </c>
       <c r="R9" t="n">
-        <v>6555301</v>
+        <v>6555397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1602,7 +1600,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121439066</v>
+        <v>121434240</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>8425</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,27 +1644,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1674,10 +1673,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640409</v>
+        <v>640418</v>
       </c>
       <c r="R10" t="n">
-        <v>6555499</v>
+        <v>6555513</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,10 +1746,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121432726</v>
+        <v>121432972</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,41 +1758,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grönbrink, Grönbrink, Srm</t>
+          <t>Älmsta, Älmsta, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640426</v>
+        <v>640464</v>
       </c>
       <c r="R11" t="n">
-        <v>6555326</v>
+        <v>6555319</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1847,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121434294</v>
+        <v>121439066</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>97067</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,54 +1892,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älmsta, Älmsta, Srm</t>
+          <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640414</v>
+        <v>640409</v>
       </c>
       <c r="R12" t="n">
-        <v>6555503</v>
+        <v>6555499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1959,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,12 +1969,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,7 +1997,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121432972</v>
+        <v>121434294</v>
       </c>
       <c r="B13" t="n">
         <v>98113</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640464</v>
+        <v>640414</v>
       </c>
       <c r="R13" t="n">
-        <v>6555319</v>
+        <v>6555503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En fröställning  Växer i nord sluttningen i blockig terräng nedanför en tall.</t>
+          <t>Växer bland gamla tallar där skogen öppnar sig mot diket. Unga granar har nyligen röjts bort på platsen inför avverkning.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121552781</v>
+        <v>121551416</v>
       </c>
       <c r="B15" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2271,27 +2271,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640380</v>
+        <v>640552</v>
       </c>
       <c r="R15" t="n">
-        <v>6555545</v>
+        <v>6555567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121551416</v>
+        <v>121552781</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,27 +2388,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2417,10 +2417,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640552</v>
+        <v>640380</v>
       </c>
       <c r="R16" t="n">
-        <v>6555567</v>
+        <v>6555545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 36955-2024 artfynd.xlsx
+++ b/artfynd/A 36955-2024 artfynd.xlsx
@@ -2255,10 +2255,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121551416</v>
+        <v>121551556</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>8425</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,43 +2267,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640552</v>
+        <v>640504</v>
       </c>
       <c r="R15" t="n">
-        <v>6555567</v>
+        <v>6555547</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2335,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2340,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,7 +2367,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121552781</v>
+        <v>121551458</v>
       </c>
       <c r="B16" t="n">
         <v>57510</v>
@@ -2417,10 +2412,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640380</v>
+        <v>640527</v>
       </c>
       <c r="R16" t="n">
-        <v>6555545</v>
+        <v>6555570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2447,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2462,7 +2457,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2484,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121551458</v>
+        <v>121551416</v>
       </c>
       <c r="B17" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,27 +2500,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2534,10 +2529,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640527</v>
+        <v>640552</v>
       </c>
       <c r="R17" t="n">
-        <v>6555570</v>
+        <v>6555567</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2569,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2579,7 +2574,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121551556</v>
+        <v>121552781</v>
       </c>
       <c r="B18" t="n">
-        <v>8425</v>
+        <v>57510</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2618,38 +2613,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grönbrink, Grönbrink, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640504</v>
+        <v>640380</v>
       </c>
       <c r="R18" t="n">
-        <v>6555547</v>
+        <v>6555545</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
